--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5047,59 +5047,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129609351</v>
+        <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>91443</v>
+        <v>93083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668141</v>
+        <v>668173</v>
       </c>
       <c r="R40" t="n">
-        <v>6696401</v>
+        <v>6696465</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5123,12 +5112,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5137,83 +5126,71 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609351</t>
+          <t>https://artportalen.se/Sighting/136923491</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129609027</v>
+        <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93233</v>
+        <v>93083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668087</v>
+        <v>668185</v>
       </c>
       <c r="R41" t="n">
-        <v>6696419</v>
+        <v>6696496</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5237,12 +5214,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5251,34 +5228,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609027</t>
+          <t>https://artportalen.se/Sighting/136923492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129609091</v>
+        <v>129609351</v>
       </c>
       <c r="B42" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5286,26 +5262,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5321,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668081</v>
+        <v>668141</v>
       </c>
       <c r="R42" t="n">
-        <v>6696434</v>
+        <v>6696401</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5383,13 +5359,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609091</t>
+          <t>https://artportalen.se/Sighting/129609351</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129609296</v>
+        <v>129609027</v>
       </c>
       <c r="B43" t="n">
         <v>93233</v>
@@ -5419,7 +5395,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5435,10 +5411,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668139</v>
+        <v>668087</v>
       </c>
       <c r="R43" t="n">
-        <v>6696414</v>
+        <v>6696419</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5497,13 +5473,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609296</t>
+          <t>https://artportalen.se/Sighting/129609027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129609299</v>
+        <v>129609091</v>
       </c>
       <c r="B44" t="n">
         <v>93233</v>
@@ -5549,13 +5525,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668139</v>
+        <v>668081</v>
       </c>
       <c r="R44" t="n">
-        <v>6696407</v>
+        <v>6696434</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5611,13 +5587,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609299</t>
+          <t>https://artportalen.se/Sighting/129609091</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129609313</v>
+        <v>129609296</v>
       </c>
       <c r="B45" t="n">
         <v>93233</v>
@@ -5647,7 +5623,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5663,13 +5639,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668144</v>
+        <v>668139</v>
       </c>
       <c r="R45" t="n">
-        <v>6696410</v>
+        <v>6696414</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5725,13 +5701,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609313</t>
+          <t>https://artportalen.se/Sighting/129609296</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129609318</v>
+        <v>129609299</v>
       </c>
       <c r="B46" t="n">
         <v>93233</v>
@@ -5761,7 +5737,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5777,13 +5753,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668134</v>
+        <v>668139</v>
       </c>
       <c r="R46" t="n">
-        <v>6696397</v>
+        <v>6696407</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5839,13 +5815,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609318</t>
+          <t>https://artportalen.se/Sighting/129609299</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129609708</v>
+        <v>129609313</v>
       </c>
       <c r="B47" t="n">
         <v>93233</v>
@@ -5875,7 +5851,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5891,13 +5867,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668182</v>
+        <v>668144</v>
       </c>
       <c r="R47" t="n">
-        <v>6696450</v>
+        <v>6696410</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5953,13 +5929,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609708</t>
+          <t>https://artportalen.se/Sighting/129609313</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129610357</v>
+        <v>129609318</v>
       </c>
       <c r="B48" t="n">
         <v>93233</v>
@@ -5989,7 +5965,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6005,13 +5981,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668132</v>
+        <v>668134</v>
       </c>
       <c r="R48" t="n">
-        <v>6696568</v>
+        <v>6696397</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6067,16 +6043,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129610357</t>
+          <t>https://artportalen.se/Sighting/129609318</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129680912</v>
+        <v>129609708</v>
       </c>
       <c r="B49" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6103,7 +6079,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6119,13 +6095,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668159</v>
+        <v>668182</v>
       </c>
       <c r="R49" t="n">
-        <v>6696523</v>
+        <v>6696450</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,12 +6125,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6181,13 +6157,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129680912</t>
+          <t>https://artportalen.se/Sighting/129609708</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129680938</v>
+        <v>129610357</v>
       </c>
       <c r="B50" t="n">
         <v>93233</v>
@@ -6217,7 +6193,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6233,10 +6209,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668148</v>
+        <v>668132</v>
       </c>
       <c r="R50" t="n">
-        <v>6696556</v>
+        <v>6696568</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6263,12 +6239,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6295,59 +6271,65 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129680938</t>
+          <t>https://artportalen.se/Sighting/129610357</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132466244</v>
+        <v>129680912</v>
       </c>
       <c r="B51" t="n">
-        <v>58349</v>
+        <v>93307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668150</v>
+        <v>668159</v>
       </c>
       <c r="R51" t="n">
-        <v>6696399</v>
+        <v>6696523</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6371,12 +6353,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6385,70 +6367,69 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132466244</t>
+          <t>https://artportalen.se/Sighting/129680912</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129609007</v>
+        <v>129680938</v>
       </c>
       <c r="B52" t="n">
-        <v>58817</v>
+        <v>93233</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6456,10 +6437,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668099</v>
+        <v>668148</v>
       </c>
       <c r="R52" t="n">
-        <v>6696406</v>
+        <v>6696556</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6486,12 +6467,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,38 +6499,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609007</t>
+          <t>https://artportalen.se/Sighting/129680938</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208775</v>
+        <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>99096</v>
+        <v>93447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6559,10 +6540,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668180</v>
+        <v>668164</v>
       </c>
       <c r="R53" t="n">
-        <v>6696501</v>
+        <v>6696524</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,12 +6570,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6620,16 +6601,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120208775</t>
+          <t>https://artportalen.se/Sighting/136923493</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208776</v>
+        <v>132466244</v>
       </c>
       <c r="B54" t="n">
-        <v>99096</v>
+        <v>58349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,37 +6618,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668186</v>
+        <v>668150</v>
       </c>
       <c r="R54" t="n">
-        <v>6696508</v>
+        <v>6696399</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6691,12 +6677,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6722,16 +6708,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120208776</t>
+          <t>https://artportalen.se/Sighting/132466244</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129609173</v>
+        <v>129609007</v>
       </c>
       <c r="B55" t="n">
-        <v>99096</v>
+        <v>58817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,31 +6725,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>208249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6771,10 +6762,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668102</v>
+        <v>668099</v>
       </c>
       <c r="R55" t="n">
-        <v>6696465</v>
+        <v>6696406</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6833,13 +6824,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609173</t>
+          <t>https://artportalen.se/Sighting/129609007</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129609694</v>
+        <v>120208775</v>
       </c>
       <c r="B56" t="n">
         <v>99096</v>
@@ -6868,27 +6859,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668168</v>
+        <v>668180</v>
       </c>
       <c r="R56" t="n">
-        <v>6696425</v>
+        <v>6696501</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6912,12 +6895,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6926,31 +6909,30 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609694</t>
+          <t>https://artportalen.se/Sighting/120208775</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129609702</v>
+        <v>120208776</v>
       </c>
       <c r="B57" t="n">
         <v>99096</v>
@@ -6979,23 +6961,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668182</v>
+        <v>668186</v>
       </c>
       <c r="R57" t="n">
-        <v>6696446</v>
+        <v>6696508</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7019,12 +6997,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7033,31 +7011,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609702</t>
+          <t>https://artportalen.se/Sighting/120208776</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129609896</v>
+        <v>129609173</v>
       </c>
       <c r="B58" t="n">
         <v>99096</v>
@@ -7087,7 +7064,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7096,13 +7077,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668165</v>
+        <v>668102</v>
       </c>
       <c r="R58" t="n">
-        <v>6696493</v>
+        <v>6696465</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7158,16 +7139,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609896</t>
+          <t>https://artportalen.se/Sighting/129609173</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129609756</v>
+        <v>129609694</v>
       </c>
       <c r="B59" t="n">
-        <v>99153</v>
+        <v>99096</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,33 +7156,25 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -7215,10 +7188,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668198</v>
+        <v>668168</v>
       </c>
       <c r="R59" t="n">
-        <v>6696457</v>
+        <v>6696425</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7277,16 +7250,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609756</t>
+          <t>https://artportalen.se/Sighting/129609694</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129609743</v>
+        <v>129609702</v>
       </c>
       <c r="B60" t="n">
-        <v>106155</v>
+        <v>99096</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7294,21 +7267,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7322,10 +7295,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668198</v>
+        <v>668182</v>
       </c>
       <c r="R60" t="n">
-        <v>6696456</v>
+        <v>6696446</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7384,16 +7357,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609743</t>
+          <t>https://artportalen.se/Sighting/129609702</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132466278</v>
+        <v>129609896</v>
       </c>
       <c r="B61" t="n">
-        <v>106236</v>
+        <v>99096</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7401,37 +7374,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668161</v>
+        <v>668165</v>
       </c>
       <c r="R61" t="n">
-        <v>6696451</v>
+        <v>6696493</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7455,12 +7432,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7469,71 +7446,88 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132466278</t>
+          <t>https://artportalen.se/Sighting/129609896</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208682</v>
+        <v>129609756</v>
       </c>
       <c r="B62" t="n">
-        <v>102241</v>
+        <v>99153</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>219874</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668186</v>
+        <v>668198</v>
       </c>
       <c r="R62" t="n">
-        <v>6696508</v>
+        <v>6696457</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7557,12 +7551,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7571,33 +7565,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120208682</t>
+          <t>https://artportalen.se/Sighting/129609756</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129608936</v>
+        <v>129609743</v>
       </c>
       <c r="B63" t="n">
-        <v>97977</v>
+        <v>106155</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7605,19 +7600,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221944</v>
+        <v>221141</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -7629,13 +7628,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668116</v>
+        <v>668198</v>
       </c>
       <c r="R63" t="n">
-        <v>6696401</v>
+        <v>6696456</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7691,16 +7690,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129608936</t>
+          <t>https://artportalen.se/Sighting/129609743</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208739</v>
+        <v>132466278</v>
       </c>
       <c r="B64" t="n">
-        <v>104628</v>
+        <v>106236</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7708,16 +7707,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222412</v>
+        <v>221141</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7732,13 +7731,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668166</v>
+        <v>668161</v>
       </c>
       <c r="R64" t="n">
-        <v>6696498</v>
+        <v>6696451</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7762,12 +7761,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7793,63 +7792,51 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120208739</t>
+          <t>https://artportalen.se/Sighting/132466278</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129609325</v>
+        <v>120208682</v>
       </c>
       <c r="B65" t="n">
-        <v>104627</v>
+        <v>102241</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668136</v>
+        <v>668186</v>
       </c>
       <c r="R65" t="n">
-        <v>6696404</v>
+        <v>6696508</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7876,12 +7863,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7890,34 +7877,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609325</t>
+          <t>https://artportalen.se/Sighting/120208682</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124393207</v>
+        <v>129608936</v>
       </c>
       <c r="B66" t="n">
-        <v>101326</v>
+        <v>97977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7925,37 +7911,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668159</v>
+        <v>668116</v>
       </c>
       <c r="R66" t="n">
-        <v>6696419</v>
+        <v>6696401</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7979,12 +7965,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7993,33 +7979,34 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124393207</t>
+          <t>https://artportalen.se/Sighting/129608936</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124393208</v>
+        <v>120208739</v>
       </c>
       <c r="B67" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8027,21 +8014,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8051,13 +8038,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668133</v>
+        <v>668166</v>
       </c>
       <c r="R67" t="n">
-        <v>6696416</v>
+        <v>6696498</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8081,12 +8068,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8112,16 +8099,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124393208</t>
+          <t>https://artportalen.se/Sighting/120208739</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129608923</v>
+        <v>129609325</v>
       </c>
       <c r="B68" t="n">
-        <v>101325</v>
+        <v>104627</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8129,25 +8116,33 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -8157,10 +8152,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668123</v>
+        <v>668136</v>
       </c>
       <c r="R68" t="n">
-        <v>6696411</v>
+        <v>6696404</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8219,16 +8214,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129608923</t>
+          <t>https://artportalen.se/Sighting/129609325</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129609001</v>
+        <v>124393207</v>
       </c>
       <c r="B69" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8254,23 +8249,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668099</v>
+        <v>668159</v>
       </c>
       <c r="R69" t="n">
-        <v>6696406</v>
+        <v>6696419</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8294,12 +8285,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8308,34 +8299,33 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609001</t>
+          <t>https://artportalen.se/Sighting/124393207</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129609073</v>
+        <v>124393208</v>
       </c>
       <c r="B70" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8361,23 +8351,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668078</v>
+        <v>668133</v>
       </c>
       <c r="R70" t="n">
-        <v>6696419</v>
+        <v>6696416</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8401,12 +8387,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8415,31 +8401,30 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609073</t>
+          <t>https://artportalen.se/Sighting/124393208</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129609100</v>
+        <v>129608923</v>
       </c>
       <c r="B71" t="n">
         <v>101325</v>
@@ -8478,10 +8463,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668105</v>
+        <v>668123</v>
       </c>
       <c r="R71" t="n">
-        <v>6696449</v>
+        <v>6696411</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8540,13 +8525,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609100</t>
+          <t>https://artportalen.se/Sighting/129608923</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129609244</v>
+        <v>129609001</v>
       </c>
       <c r="B72" t="n">
         <v>101325</v>
@@ -8585,13 +8570,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668097</v>
+        <v>668099</v>
       </c>
       <c r="R72" t="n">
-        <v>6696476</v>
+        <v>6696406</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8647,13 +8632,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609244</t>
+          <t>https://artportalen.se/Sighting/129609001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129609548</v>
+        <v>129609073</v>
       </c>
       <c r="B73" t="n">
         <v>101325</v>
@@ -8692,10 +8677,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668152</v>
+        <v>668078</v>
       </c>
       <c r="R73" t="n">
-        <v>6696412</v>
+        <v>6696419</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8754,13 +8739,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609548</t>
+          <t>https://artportalen.se/Sighting/129609073</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129609695</v>
+        <v>129609100</v>
       </c>
       <c r="B74" t="n">
         <v>101325</v>
@@ -8799,13 +8784,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668168</v>
+        <v>668105</v>
       </c>
       <c r="R74" t="n">
-        <v>6696425</v>
+        <v>6696449</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8861,13 +8846,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609695</t>
+          <t>https://artportalen.se/Sighting/129609100</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129609751</v>
+        <v>129609244</v>
       </c>
       <c r="B75" t="n">
         <v>101325</v>
@@ -8906,13 +8891,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668198</v>
+        <v>668097</v>
       </c>
       <c r="R75" t="n">
-        <v>6696456</v>
+        <v>6696476</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8968,16 +8953,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609751</t>
+          <t>https://artportalen.se/Sighting/129609244</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132466301</v>
+        <v>129609548</v>
       </c>
       <c r="B76" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9003,19 +8988,23 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668162</v>
+        <v>668152</v>
       </c>
       <c r="R76" t="n">
-        <v>6696453</v>
+        <v>6696412</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9039,12 +9028,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9053,33 +9042,34 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132466301</t>
+          <t>https://artportalen.se/Sighting/129609548</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132466303</v>
+        <v>129609695</v>
       </c>
       <c r="B77" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9105,19 +9095,23 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668165</v>
+        <v>668168</v>
       </c>
       <c r="R77" t="n">
-        <v>6696429</v>
+        <v>6696425</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9141,12 +9135,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9155,33 +9149,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132466303</t>
+          <t>https://artportalen.se/Sighting/129609695</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129609783</v>
+        <v>129609751</v>
       </c>
       <c r="B78" t="n">
-        <v>89141</v>
+        <v>101325</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9189,34 +9184,27 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>239209</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9224,13 +9212,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668212</v>
+        <v>668198</v>
       </c>
       <c r="R78" t="n">
-        <v>6696450</v>
+        <v>6696456</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9257,19 +9245,9 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9282,11 +9260,6 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
@@ -9301,65 +9274,54 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129609783</t>
+          <t>https://artportalen.se/Sighting/129609751</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129680905</v>
+        <v>132466301</v>
       </c>
       <c r="B79" t="n">
-        <v>87346</v>
+        <v>101403</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668149</v>
+        <v>668162</v>
       </c>
       <c r="R79" t="n">
-        <v>6696518</v>
+        <v>6696453</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9383,22 +9345,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9407,88 +9359,71 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129680905</t>
+          <t>https://artportalen.se/Sighting/132466301</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129707800</v>
+        <v>132466303</v>
       </c>
       <c r="B80" t="n">
-        <v>87312</v>
+        <v>101403</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6037417</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668173</v>
+        <v>668165</v>
       </c>
       <c r="R80" t="n">
-        <v>6696522</v>
+        <v>6696429</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9512,22 +9447,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9536,75 +9461,60 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Hotspot; kalkbarrskog; Under gran</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129707800</t>
+          <t>https://artportalen.se/Sighting/132466303</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129609164</v>
+        <v>129609783</v>
       </c>
       <c r="B81" t="n">
-        <v>91445</v>
+        <v>89141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6039940</v>
+        <v>239209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9620,13 +9530,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668099</v>
+        <v>668212</v>
       </c>
       <c r="R81" t="n">
-        <v>6696458</v>
+        <v>6696450</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9655,7 +9565,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9665,7 +9575,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9674,18 +9584,9 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; under gran och björk</t>
-        </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
@@ -9705,6 +9606,411 @@
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129609783</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129680905</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>668149</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6696518</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680905</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129707800</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>668173</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6696522</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Hotspot; kalkbarrskog; Under gran</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129707800</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129609164</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91445</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6039940</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mandarinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ramaria tridentina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>668099</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6696458</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; under gran och björk</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129609164</t>
         </is>
@@ -9792,6 +10098,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29564-2023 artfynd.xlsx
+++ b/artfynd/A 29564-2023 artfynd.xlsx
@@ -5050,7 +5050,7 @@
         <v>136923491</v>
       </c>
       <c r="B40" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136923492</v>
       </c>
       <c r="B41" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136923493</v>
       </c>
       <c r="B53" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
